--- a/reports/ai_readiness_2026-W20.xlsx
+++ b/reports/ai_readiness_2026-W20.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-12 11:56 UTC</t>
+          <t>Generated: 2026-05-15 18:11 UTC</t>
         </is>
       </c>
     </row>
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40.5</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -511,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -655,7 +655,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -665,7 +665,7 @@
         <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
@@ -841,7 +841,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Tell Mel</t>
+          <t>Tellmel</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -859,17 +859,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Timeout</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
@@ -888,7 +888,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -903,7 +903,109 @@
         <v>100</v>
       </c>
       <c r="H11" t="n">
-        <v>70</v>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>100</v>
+      </c>
+      <c r="G13" t="n">
+        <v>100</v>
+      </c>
+      <c r="H13" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>friend.com</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>100</v>
+      </c>
+      <c r="G14" t="n">
+        <v>100</v>
+      </c>
+      <c r="H14" t="n">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -917,7 +1019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -936,7 +1038,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-12 11:56 UTC</t>
+          <t>Generated: 2026-05-15 18:11 UTC</t>
         </is>
       </c>
     </row>
@@ -1005,10 +1107,10 @@
         <v>70</v>
       </c>
       <c r="C7" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="D7" t="n">
-        <v>-30</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="8">
@@ -1094,17 +1196,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Tell Mel</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
+          <t>Tellmel</t>
+        </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-15</v>
+        <v>40</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1117,10 +1218,55 @@
         <v>40</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="D14" t="n">
-        <v>30</v>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>15</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>40</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>friend.com</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>40</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
   </sheetData>
